--- a/01. Preprocessing data/data_CSV/02_US.xlsx
+++ b/01. Preprocessing data/data_CSV/02_US.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="5" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="4" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Discr" sheetId="1" r:id="rId1"/>
@@ -16,10 +16,12 @@
     <sheet name="USformationBloodFlow" sheetId="7" r:id="rId7"/>
     <sheet name="USelastography" sheetId="8" r:id="rId8"/>
     <sheet name="USdiagnosis" sheetId="9" r:id="rId9"/>
+    <sheet name="UScalcinatesMicroPure" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Discr!$A$1:$I$599</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">USbackground!$A$1:$C$601</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">UScalcinatesMicroPure!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">USdiagnosis!$A$1:$C$609</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">USelastography!$A$1:$C$600</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">USformation!$A$1:$C$661</definedName>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11013" uniqueCount="1283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12212" uniqueCount="1882">
   <si>
     <t>EMC4541406</t>
   </si>
@@ -3887,6 +3889,1803 @@
   </si>
   <si>
     <t>IDusDiscr</t>
+  </si>
+  <si>
+    <t>UScalcinatesMicroPure</t>
+  </si>
+  <si>
+    <t>id1</t>
+  </si>
+  <si>
+    <t>id2</t>
+  </si>
+  <si>
+    <t>id3</t>
+  </si>
+  <si>
+    <t>id4</t>
+  </si>
+  <si>
+    <t>id5</t>
+  </si>
+  <si>
+    <t>id6</t>
+  </si>
+  <si>
+    <t>id7</t>
+  </si>
+  <si>
+    <t>id8</t>
+  </si>
+  <si>
+    <t>id9</t>
+  </si>
+  <si>
+    <t>id10</t>
+  </si>
+  <si>
+    <t>id11</t>
+  </si>
+  <si>
+    <t>id12</t>
+  </si>
+  <si>
+    <t>id13</t>
+  </si>
+  <si>
+    <t>id14</t>
+  </si>
+  <si>
+    <t>id15</t>
+  </si>
+  <si>
+    <t>id16</t>
+  </si>
+  <si>
+    <t>id17</t>
+  </si>
+  <si>
+    <t>id18</t>
+  </si>
+  <si>
+    <t>id19</t>
+  </si>
+  <si>
+    <t>id20</t>
+  </si>
+  <si>
+    <t>id21</t>
+  </si>
+  <si>
+    <t>id22</t>
+  </si>
+  <si>
+    <t>id23</t>
+  </si>
+  <si>
+    <t>id24</t>
+  </si>
+  <si>
+    <t>id25</t>
+  </si>
+  <si>
+    <t>id26</t>
+  </si>
+  <si>
+    <t>id27</t>
+  </si>
+  <si>
+    <t>id28</t>
+  </si>
+  <si>
+    <t>id29</t>
+  </si>
+  <si>
+    <t>id30</t>
+  </si>
+  <si>
+    <t>id31</t>
+  </si>
+  <si>
+    <t>id32</t>
+  </si>
+  <si>
+    <t>id33</t>
+  </si>
+  <si>
+    <t>id34</t>
+  </si>
+  <si>
+    <t>id35</t>
+  </si>
+  <si>
+    <t>id36</t>
+  </si>
+  <si>
+    <t>id37</t>
+  </si>
+  <si>
+    <t>id38</t>
+  </si>
+  <si>
+    <t>id39</t>
+  </si>
+  <si>
+    <t>id40</t>
+  </si>
+  <si>
+    <t>id41</t>
+  </si>
+  <si>
+    <t>id42</t>
+  </si>
+  <si>
+    <t>id43</t>
+  </si>
+  <si>
+    <t>id44</t>
+  </si>
+  <si>
+    <t>id45</t>
+  </si>
+  <si>
+    <t>id46</t>
+  </si>
+  <si>
+    <t>id47</t>
+  </si>
+  <si>
+    <t>id48</t>
+  </si>
+  <si>
+    <t>id49</t>
+  </si>
+  <si>
+    <t>id50</t>
+  </si>
+  <si>
+    <t>id51</t>
+  </si>
+  <si>
+    <t>id52</t>
+  </si>
+  <si>
+    <t>id53</t>
+  </si>
+  <si>
+    <t>id54</t>
+  </si>
+  <si>
+    <t>id55</t>
+  </si>
+  <si>
+    <t>id56</t>
+  </si>
+  <si>
+    <t>id57</t>
+  </si>
+  <si>
+    <t>id58</t>
+  </si>
+  <si>
+    <t>id59</t>
+  </si>
+  <si>
+    <t>id60</t>
+  </si>
+  <si>
+    <t>id61</t>
+  </si>
+  <si>
+    <t>id62</t>
+  </si>
+  <si>
+    <t>id63</t>
+  </si>
+  <si>
+    <t>id64</t>
+  </si>
+  <si>
+    <t>id65</t>
+  </si>
+  <si>
+    <t>id66</t>
+  </si>
+  <si>
+    <t>id67</t>
+  </si>
+  <si>
+    <t>id68</t>
+  </si>
+  <si>
+    <t>id69</t>
+  </si>
+  <si>
+    <t>id70</t>
+  </si>
+  <si>
+    <t>id71</t>
+  </si>
+  <si>
+    <t>id72</t>
+  </si>
+  <si>
+    <t>id73</t>
+  </si>
+  <si>
+    <t>id74</t>
+  </si>
+  <si>
+    <t>id75</t>
+  </si>
+  <si>
+    <t>id76</t>
+  </si>
+  <si>
+    <t>id77</t>
+  </si>
+  <si>
+    <t>id78</t>
+  </si>
+  <si>
+    <t>id79</t>
+  </si>
+  <si>
+    <t>id80</t>
+  </si>
+  <si>
+    <t>id81</t>
+  </si>
+  <si>
+    <t>id82</t>
+  </si>
+  <si>
+    <t>id83</t>
+  </si>
+  <si>
+    <t>id84</t>
+  </si>
+  <si>
+    <t>id85</t>
+  </si>
+  <si>
+    <t>id86</t>
+  </si>
+  <si>
+    <t>id87</t>
+  </si>
+  <si>
+    <t>id88</t>
+  </si>
+  <si>
+    <t>id89</t>
+  </si>
+  <si>
+    <t>id90</t>
+  </si>
+  <si>
+    <t>id91</t>
+  </si>
+  <si>
+    <t>id92</t>
+  </si>
+  <si>
+    <t>id93</t>
+  </si>
+  <si>
+    <t>id94</t>
+  </si>
+  <si>
+    <t>id95</t>
+  </si>
+  <si>
+    <t>id96</t>
+  </si>
+  <si>
+    <t>id97</t>
+  </si>
+  <si>
+    <t>id98</t>
+  </si>
+  <si>
+    <t>id99</t>
+  </si>
+  <si>
+    <t>id100</t>
+  </si>
+  <si>
+    <t>id101</t>
+  </si>
+  <si>
+    <t>id102</t>
+  </si>
+  <si>
+    <t>id103</t>
+  </si>
+  <si>
+    <t>id104</t>
+  </si>
+  <si>
+    <t>id105</t>
+  </si>
+  <si>
+    <t>id106</t>
+  </si>
+  <si>
+    <t>id107</t>
+  </si>
+  <si>
+    <t>id108</t>
+  </si>
+  <si>
+    <t>id109</t>
+  </si>
+  <si>
+    <t>id110</t>
+  </si>
+  <si>
+    <t>id111</t>
+  </si>
+  <si>
+    <t>id112</t>
+  </si>
+  <si>
+    <t>id113</t>
+  </si>
+  <si>
+    <t>id114</t>
+  </si>
+  <si>
+    <t>id115</t>
+  </si>
+  <si>
+    <t>id116</t>
+  </si>
+  <si>
+    <t>id117</t>
+  </si>
+  <si>
+    <t>id118</t>
+  </si>
+  <si>
+    <t>id119</t>
+  </si>
+  <si>
+    <t>id120</t>
+  </si>
+  <si>
+    <t>id121</t>
+  </si>
+  <si>
+    <t>id122</t>
+  </si>
+  <si>
+    <t>id123</t>
+  </si>
+  <si>
+    <t>id124</t>
+  </si>
+  <si>
+    <t>id125</t>
+  </si>
+  <si>
+    <t>id126</t>
+  </si>
+  <si>
+    <t>id127</t>
+  </si>
+  <si>
+    <t>id128</t>
+  </si>
+  <si>
+    <t>id129</t>
+  </si>
+  <si>
+    <t>id130</t>
+  </si>
+  <si>
+    <t>id131</t>
+  </si>
+  <si>
+    <t>id132</t>
+  </si>
+  <si>
+    <t>id133</t>
+  </si>
+  <si>
+    <t>id134</t>
+  </si>
+  <si>
+    <t>id135</t>
+  </si>
+  <si>
+    <t>id136</t>
+  </si>
+  <si>
+    <t>id137</t>
+  </si>
+  <si>
+    <t>id138</t>
+  </si>
+  <si>
+    <t>id139</t>
+  </si>
+  <si>
+    <t>id140</t>
+  </si>
+  <si>
+    <t>id141</t>
+  </si>
+  <si>
+    <t>id142</t>
+  </si>
+  <si>
+    <t>id143</t>
+  </si>
+  <si>
+    <t>id144</t>
+  </si>
+  <si>
+    <t>id145</t>
+  </si>
+  <si>
+    <t>id146</t>
+  </si>
+  <si>
+    <t>id147</t>
+  </si>
+  <si>
+    <t>id148</t>
+  </si>
+  <si>
+    <t>id149</t>
+  </si>
+  <si>
+    <t>id150</t>
+  </si>
+  <si>
+    <t>id151</t>
+  </si>
+  <si>
+    <t>id152</t>
+  </si>
+  <si>
+    <t>id153</t>
+  </si>
+  <si>
+    <t>id154</t>
+  </si>
+  <si>
+    <t>id155</t>
+  </si>
+  <si>
+    <t>id156</t>
+  </si>
+  <si>
+    <t>id157</t>
+  </si>
+  <si>
+    <t>id158</t>
+  </si>
+  <si>
+    <t>id159</t>
+  </si>
+  <si>
+    <t>id160</t>
+  </si>
+  <si>
+    <t>id161</t>
+  </si>
+  <si>
+    <t>id162</t>
+  </si>
+  <si>
+    <t>id163</t>
+  </si>
+  <si>
+    <t>id164</t>
+  </si>
+  <si>
+    <t>id165</t>
+  </si>
+  <si>
+    <t>id166</t>
+  </si>
+  <si>
+    <t>id167</t>
+  </si>
+  <si>
+    <t>id168</t>
+  </si>
+  <si>
+    <t>id169</t>
+  </si>
+  <si>
+    <t>id170</t>
+  </si>
+  <si>
+    <t>id171</t>
+  </si>
+  <si>
+    <t>id172</t>
+  </si>
+  <si>
+    <t>id173</t>
+  </si>
+  <si>
+    <t>id174</t>
+  </si>
+  <si>
+    <t>id175</t>
+  </si>
+  <si>
+    <t>id176</t>
+  </si>
+  <si>
+    <t>id177</t>
+  </si>
+  <si>
+    <t>id178</t>
+  </si>
+  <si>
+    <t>id179</t>
+  </si>
+  <si>
+    <t>id180</t>
+  </si>
+  <si>
+    <t>id181</t>
+  </si>
+  <si>
+    <t>id182</t>
+  </si>
+  <si>
+    <t>id183</t>
+  </si>
+  <si>
+    <t>id184</t>
+  </si>
+  <si>
+    <t>id185</t>
+  </si>
+  <si>
+    <t>id186</t>
+  </si>
+  <si>
+    <t>id187</t>
+  </si>
+  <si>
+    <t>id188</t>
+  </si>
+  <si>
+    <t>id189</t>
+  </si>
+  <si>
+    <t>id190</t>
+  </si>
+  <si>
+    <t>id191</t>
+  </si>
+  <si>
+    <t>id192</t>
+  </si>
+  <si>
+    <t>id193</t>
+  </si>
+  <si>
+    <t>id194</t>
+  </si>
+  <si>
+    <t>id195</t>
+  </si>
+  <si>
+    <t>id196</t>
+  </si>
+  <si>
+    <t>id197</t>
+  </si>
+  <si>
+    <t>id198</t>
+  </si>
+  <si>
+    <t>id199</t>
+  </si>
+  <si>
+    <t>id200</t>
+  </si>
+  <si>
+    <t>id201</t>
+  </si>
+  <si>
+    <t>id202</t>
+  </si>
+  <si>
+    <t>id203</t>
+  </si>
+  <si>
+    <t>id204</t>
+  </si>
+  <si>
+    <t>id205</t>
+  </si>
+  <si>
+    <t>id206</t>
+  </si>
+  <si>
+    <t>id207</t>
+  </si>
+  <si>
+    <t>id208</t>
+  </si>
+  <si>
+    <t>id209</t>
+  </si>
+  <si>
+    <t>id210</t>
+  </si>
+  <si>
+    <t>id211</t>
+  </si>
+  <si>
+    <t>id212</t>
+  </si>
+  <si>
+    <t>id213</t>
+  </si>
+  <si>
+    <t>id214</t>
+  </si>
+  <si>
+    <t>id215</t>
+  </si>
+  <si>
+    <t>id216</t>
+  </si>
+  <si>
+    <t>id217</t>
+  </si>
+  <si>
+    <t>id218</t>
+  </si>
+  <si>
+    <t>id219</t>
+  </si>
+  <si>
+    <t>id220</t>
+  </si>
+  <si>
+    <t>id221</t>
+  </si>
+  <si>
+    <t>id222</t>
+  </si>
+  <si>
+    <t>id223</t>
+  </si>
+  <si>
+    <t>id224</t>
+  </si>
+  <si>
+    <t>id225</t>
+  </si>
+  <si>
+    <t>id226</t>
+  </si>
+  <si>
+    <t>id227</t>
+  </si>
+  <si>
+    <t>id228</t>
+  </si>
+  <si>
+    <t>id229</t>
+  </si>
+  <si>
+    <t>id230</t>
+  </si>
+  <si>
+    <t>id231</t>
+  </si>
+  <si>
+    <t>id232</t>
+  </si>
+  <si>
+    <t>id233</t>
+  </si>
+  <si>
+    <t>id234</t>
+  </si>
+  <si>
+    <t>id235</t>
+  </si>
+  <si>
+    <t>id236</t>
+  </si>
+  <si>
+    <t>id237</t>
+  </si>
+  <si>
+    <t>id238</t>
+  </si>
+  <si>
+    <t>id239</t>
+  </si>
+  <si>
+    <t>id240</t>
+  </si>
+  <si>
+    <t>id241</t>
+  </si>
+  <si>
+    <t>id242</t>
+  </si>
+  <si>
+    <t>id243</t>
+  </si>
+  <si>
+    <t>id244</t>
+  </si>
+  <si>
+    <t>id245</t>
+  </si>
+  <si>
+    <t>id246</t>
+  </si>
+  <si>
+    <t>id247</t>
+  </si>
+  <si>
+    <t>id248</t>
+  </si>
+  <si>
+    <t>id249</t>
+  </si>
+  <si>
+    <t>id250</t>
+  </si>
+  <si>
+    <t>id251</t>
+  </si>
+  <si>
+    <t>id252</t>
+  </si>
+  <si>
+    <t>id253</t>
+  </si>
+  <si>
+    <t>id254</t>
+  </si>
+  <si>
+    <t>id255</t>
+  </si>
+  <si>
+    <t>id256</t>
+  </si>
+  <si>
+    <t>id257</t>
+  </si>
+  <si>
+    <t>id258</t>
+  </si>
+  <si>
+    <t>id259</t>
+  </si>
+  <si>
+    <t>id260</t>
+  </si>
+  <si>
+    <t>id261</t>
+  </si>
+  <si>
+    <t>id262</t>
+  </si>
+  <si>
+    <t>id263</t>
+  </si>
+  <si>
+    <t>id264</t>
+  </si>
+  <si>
+    <t>id265</t>
+  </si>
+  <si>
+    <t>id266</t>
+  </si>
+  <si>
+    <t>id267</t>
+  </si>
+  <si>
+    <t>id268</t>
+  </si>
+  <si>
+    <t>id269</t>
+  </si>
+  <si>
+    <t>id270</t>
+  </si>
+  <si>
+    <t>id271</t>
+  </si>
+  <si>
+    <t>id272</t>
+  </si>
+  <si>
+    <t>id273</t>
+  </si>
+  <si>
+    <t>id274</t>
+  </si>
+  <si>
+    <t>id275</t>
+  </si>
+  <si>
+    <t>id276</t>
+  </si>
+  <si>
+    <t>id277</t>
+  </si>
+  <si>
+    <t>id278</t>
+  </si>
+  <si>
+    <t>id279</t>
+  </si>
+  <si>
+    <t>id280</t>
+  </si>
+  <si>
+    <t>id281</t>
+  </si>
+  <si>
+    <t>id282</t>
+  </si>
+  <si>
+    <t>id283</t>
+  </si>
+  <si>
+    <t>id284</t>
+  </si>
+  <si>
+    <t>id285</t>
+  </si>
+  <si>
+    <t>id286</t>
+  </si>
+  <si>
+    <t>id287</t>
+  </si>
+  <si>
+    <t>id288</t>
+  </si>
+  <si>
+    <t>id289</t>
+  </si>
+  <si>
+    <t>id290</t>
+  </si>
+  <si>
+    <t>id291</t>
+  </si>
+  <si>
+    <t>id292</t>
+  </si>
+  <si>
+    <t>id293</t>
+  </si>
+  <si>
+    <t>id294</t>
+  </si>
+  <si>
+    <t>id295</t>
+  </si>
+  <si>
+    <t>id296</t>
+  </si>
+  <si>
+    <t>id297</t>
+  </si>
+  <si>
+    <t>id298</t>
+  </si>
+  <si>
+    <t>id299</t>
+  </si>
+  <si>
+    <t>id300</t>
+  </si>
+  <si>
+    <t>id301</t>
+  </si>
+  <si>
+    <t>id302</t>
+  </si>
+  <si>
+    <t>id303</t>
+  </si>
+  <si>
+    <t>id304</t>
+  </si>
+  <si>
+    <t>id305</t>
+  </si>
+  <si>
+    <t>id306</t>
+  </si>
+  <si>
+    <t>id307</t>
+  </si>
+  <si>
+    <t>id308</t>
+  </si>
+  <si>
+    <t>id309</t>
+  </si>
+  <si>
+    <t>id310</t>
+  </si>
+  <si>
+    <t>id311</t>
+  </si>
+  <si>
+    <t>id312</t>
+  </si>
+  <si>
+    <t>id313</t>
+  </si>
+  <si>
+    <t>id314</t>
+  </si>
+  <si>
+    <t>id315</t>
+  </si>
+  <si>
+    <t>id316</t>
+  </si>
+  <si>
+    <t>id317</t>
+  </si>
+  <si>
+    <t>id318</t>
+  </si>
+  <si>
+    <t>id319</t>
+  </si>
+  <si>
+    <t>id320</t>
+  </si>
+  <si>
+    <t>id321</t>
+  </si>
+  <si>
+    <t>id322</t>
+  </si>
+  <si>
+    <t>id323</t>
+  </si>
+  <si>
+    <t>id324</t>
+  </si>
+  <si>
+    <t>id325</t>
+  </si>
+  <si>
+    <t>id326</t>
+  </si>
+  <si>
+    <t>id327</t>
+  </si>
+  <si>
+    <t>id328</t>
+  </si>
+  <si>
+    <t>id329</t>
+  </si>
+  <si>
+    <t>id330</t>
+  </si>
+  <si>
+    <t>id331</t>
+  </si>
+  <si>
+    <t>id332</t>
+  </si>
+  <si>
+    <t>id333</t>
+  </si>
+  <si>
+    <t>id334</t>
+  </si>
+  <si>
+    <t>id335</t>
+  </si>
+  <si>
+    <t>id336</t>
+  </si>
+  <si>
+    <t>id337</t>
+  </si>
+  <si>
+    <t>id338</t>
+  </si>
+  <si>
+    <t>id339</t>
+  </si>
+  <si>
+    <t>id340</t>
+  </si>
+  <si>
+    <t>id341</t>
+  </si>
+  <si>
+    <t>id342</t>
+  </si>
+  <si>
+    <t>id343</t>
+  </si>
+  <si>
+    <t>id344</t>
+  </si>
+  <si>
+    <t>id345</t>
+  </si>
+  <si>
+    <t>id346</t>
+  </si>
+  <si>
+    <t>id347</t>
+  </si>
+  <si>
+    <t>id348</t>
+  </si>
+  <si>
+    <t>id349</t>
+  </si>
+  <si>
+    <t>id350</t>
+  </si>
+  <si>
+    <t>id351</t>
+  </si>
+  <si>
+    <t>id352</t>
+  </si>
+  <si>
+    <t>id353</t>
+  </si>
+  <si>
+    <t>id354</t>
+  </si>
+  <si>
+    <t>id355</t>
+  </si>
+  <si>
+    <t>id356</t>
+  </si>
+  <si>
+    <t>id357</t>
+  </si>
+  <si>
+    <t>id358</t>
+  </si>
+  <si>
+    <t>id359</t>
+  </si>
+  <si>
+    <t>id360</t>
+  </si>
+  <si>
+    <t>id361</t>
+  </si>
+  <si>
+    <t>id362</t>
+  </si>
+  <si>
+    <t>id363</t>
+  </si>
+  <si>
+    <t>id364</t>
+  </si>
+  <si>
+    <t>id365</t>
+  </si>
+  <si>
+    <t>id366</t>
+  </si>
+  <si>
+    <t>id367</t>
+  </si>
+  <si>
+    <t>id368</t>
+  </si>
+  <si>
+    <t>id369</t>
+  </si>
+  <si>
+    <t>id370</t>
+  </si>
+  <si>
+    <t>id371</t>
+  </si>
+  <si>
+    <t>id372</t>
+  </si>
+  <si>
+    <t>id373</t>
+  </si>
+  <si>
+    <t>id374</t>
+  </si>
+  <si>
+    <t>id375</t>
+  </si>
+  <si>
+    <t>id376</t>
+  </si>
+  <si>
+    <t>id377</t>
+  </si>
+  <si>
+    <t>id378</t>
+  </si>
+  <si>
+    <t>id379</t>
+  </si>
+  <si>
+    <t>id380</t>
+  </si>
+  <si>
+    <t>id381</t>
+  </si>
+  <si>
+    <t>id382</t>
+  </si>
+  <si>
+    <t>id383</t>
+  </si>
+  <si>
+    <t>id384</t>
+  </si>
+  <si>
+    <t>id385</t>
+  </si>
+  <si>
+    <t>id386</t>
+  </si>
+  <si>
+    <t>id387</t>
+  </si>
+  <si>
+    <t>id388</t>
+  </si>
+  <si>
+    <t>id389</t>
+  </si>
+  <si>
+    <t>id390</t>
+  </si>
+  <si>
+    <t>id391</t>
+  </si>
+  <si>
+    <t>id392</t>
+  </si>
+  <si>
+    <t>id393</t>
+  </si>
+  <si>
+    <t>id394</t>
+  </si>
+  <si>
+    <t>id395</t>
+  </si>
+  <si>
+    <t>id396</t>
+  </si>
+  <si>
+    <t>id397</t>
+  </si>
+  <si>
+    <t>id398</t>
+  </si>
+  <si>
+    <t>id399</t>
+  </si>
+  <si>
+    <t>id400</t>
+  </si>
+  <si>
+    <t>id401</t>
+  </si>
+  <si>
+    <t>id402</t>
+  </si>
+  <si>
+    <t>id403</t>
+  </si>
+  <si>
+    <t>id404</t>
+  </si>
+  <si>
+    <t>id405</t>
+  </si>
+  <si>
+    <t>id406</t>
+  </si>
+  <si>
+    <t>id407</t>
+  </si>
+  <si>
+    <t>id408</t>
+  </si>
+  <si>
+    <t>id409</t>
+  </si>
+  <si>
+    <t>id410</t>
+  </si>
+  <si>
+    <t>id411</t>
+  </si>
+  <si>
+    <t>id412</t>
+  </si>
+  <si>
+    <t>id413</t>
+  </si>
+  <si>
+    <t>id414</t>
+  </si>
+  <si>
+    <t>id415</t>
+  </si>
+  <si>
+    <t>id416</t>
+  </si>
+  <si>
+    <t>id417</t>
+  </si>
+  <si>
+    <t>id418</t>
+  </si>
+  <si>
+    <t>id419</t>
+  </si>
+  <si>
+    <t>id420</t>
+  </si>
+  <si>
+    <t>id421</t>
+  </si>
+  <si>
+    <t>id422</t>
+  </si>
+  <si>
+    <t>id423</t>
+  </si>
+  <si>
+    <t>id424</t>
+  </si>
+  <si>
+    <t>id425</t>
+  </si>
+  <si>
+    <t>id426</t>
+  </si>
+  <si>
+    <t>id427</t>
+  </si>
+  <si>
+    <t>id428</t>
+  </si>
+  <si>
+    <t>id429</t>
+  </si>
+  <si>
+    <t>id430</t>
+  </si>
+  <si>
+    <t>id431</t>
+  </si>
+  <si>
+    <t>id432</t>
+  </si>
+  <si>
+    <t>id433</t>
+  </si>
+  <si>
+    <t>id434</t>
+  </si>
+  <si>
+    <t>id435</t>
+  </si>
+  <si>
+    <t>id436</t>
+  </si>
+  <si>
+    <t>id437</t>
+  </si>
+  <si>
+    <t>id438</t>
+  </si>
+  <si>
+    <t>id439</t>
+  </si>
+  <si>
+    <t>id440</t>
+  </si>
+  <si>
+    <t>id441</t>
+  </si>
+  <si>
+    <t>id442</t>
+  </si>
+  <si>
+    <t>id443</t>
+  </si>
+  <si>
+    <t>id444</t>
+  </si>
+  <si>
+    <t>id445</t>
+  </si>
+  <si>
+    <t>id446</t>
+  </si>
+  <si>
+    <t>id447</t>
+  </si>
+  <si>
+    <t>id448</t>
+  </si>
+  <si>
+    <t>id449</t>
+  </si>
+  <si>
+    <t>id450</t>
+  </si>
+  <si>
+    <t>id451</t>
+  </si>
+  <si>
+    <t>id452</t>
+  </si>
+  <si>
+    <t>id453</t>
+  </si>
+  <si>
+    <t>id454</t>
+  </si>
+  <si>
+    <t>id455</t>
+  </si>
+  <si>
+    <t>id456</t>
+  </si>
+  <si>
+    <t>id457</t>
+  </si>
+  <si>
+    <t>id458</t>
+  </si>
+  <si>
+    <t>id459</t>
+  </si>
+  <si>
+    <t>id460</t>
+  </si>
+  <si>
+    <t>id461</t>
+  </si>
+  <si>
+    <t>id462</t>
+  </si>
+  <si>
+    <t>id463</t>
+  </si>
+  <si>
+    <t>id464</t>
+  </si>
+  <si>
+    <t>id465</t>
+  </si>
+  <si>
+    <t>id466</t>
+  </si>
+  <si>
+    <t>id467</t>
+  </si>
+  <si>
+    <t>id468</t>
+  </si>
+  <si>
+    <t>id469</t>
+  </si>
+  <si>
+    <t>id470</t>
+  </si>
+  <si>
+    <t>id471</t>
+  </si>
+  <si>
+    <t>id472</t>
+  </si>
+  <si>
+    <t>id473</t>
+  </si>
+  <si>
+    <t>id474</t>
+  </si>
+  <si>
+    <t>id475</t>
+  </si>
+  <si>
+    <t>id476</t>
+  </si>
+  <si>
+    <t>id477</t>
+  </si>
+  <si>
+    <t>id478</t>
+  </si>
+  <si>
+    <t>id479</t>
+  </si>
+  <si>
+    <t>id480</t>
+  </si>
+  <si>
+    <t>id481</t>
+  </si>
+  <si>
+    <t>id482</t>
+  </si>
+  <si>
+    <t>id483</t>
+  </si>
+  <si>
+    <t>id484</t>
+  </si>
+  <si>
+    <t>id485</t>
+  </si>
+  <si>
+    <t>id486</t>
+  </si>
+  <si>
+    <t>id487</t>
+  </si>
+  <si>
+    <t>id488</t>
+  </si>
+  <si>
+    <t>id489</t>
+  </si>
+  <si>
+    <t>id490</t>
+  </si>
+  <si>
+    <t>id491</t>
+  </si>
+  <si>
+    <t>id492</t>
+  </si>
+  <si>
+    <t>id493</t>
+  </si>
+  <si>
+    <t>id494</t>
+  </si>
+  <si>
+    <t>id495</t>
+  </si>
+  <si>
+    <t>id496</t>
+  </si>
+  <si>
+    <t>id497</t>
+  </si>
+  <si>
+    <t>id498</t>
+  </si>
+  <si>
+    <t>id499</t>
+  </si>
+  <si>
+    <t>id500</t>
+  </si>
+  <si>
+    <t>id501</t>
+  </si>
+  <si>
+    <t>id502</t>
+  </si>
+  <si>
+    <t>id503</t>
+  </si>
+  <si>
+    <t>id504</t>
+  </si>
+  <si>
+    <t>id505</t>
+  </si>
+  <si>
+    <t>id506</t>
+  </si>
+  <si>
+    <t>id507</t>
+  </si>
+  <si>
+    <t>id508</t>
+  </si>
+  <si>
+    <t>id509</t>
+  </si>
+  <si>
+    <t>id510</t>
+  </si>
+  <si>
+    <t>id511</t>
+  </si>
+  <si>
+    <t>id512</t>
+  </si>
+  <si>
+    <t>id513</t>
+  </si>
+  <si>
+    <t>id514</t>
+  </si>
+  <si>
+    <t>id515</t>
+  </si>
+  <si>
+    <t>id516</t>
+  </si>
+  <si>
+    <t>id517</t>
+  </si>
+  <si>
+    <t>id518</t>
+  </si>
+  <si>
+    <t>id519</t>
+  </si>
+  <si>
+    <t>id520</t>
+  </si>
+  <si>
+    <t>id521</t>
+  </si>
+  <si>
+    <t>id522</t>
+  </si>
+  <si>
+    <t>id523</t>
+  </si>
+  <si>
+    <t>id524</t>
+  </si>
+  <si>
+    <t>id525</t>
+  </si>
+  <si>
+    <t>id526</t>
+  </si>
+  <si>
+    <t>id527</t>
+  </si>
+  <si>
+    <t>id528</t>
+  </si>
+  <si>
+    <t>id529</t>
+  </si>
+  <si>
+    <t>id530</t>
+  </si>
+  <si>
+    <t>id531</t>
+  </si>
+  <si>
+    <t>id532</t>
+  </si>
+  <si>
+    <t>id533</t>
+  </si>
+  <si>
+    <t>id534</t>
+  </si>
+  <si>
+    <t>id535</t>
+  </si>
+  <si>
+    <t>id536</t>
+  </si>
+  <si>
+    <t>id537</t>
+  </si>
+  <si>
+    <t>id538</t>
+  </si>
+  <si>
+    <t>id539</t>
+  </si>
+  <si>
+    <t>id540</t>
+  </si>
+  <si>
+    <t>id541</t>
+  </si>
+  <si>
+    <t>id542</t>
+  </si>
+  <si>
+    <t>id543</t>
+  </si>
+  <si>
+    <t>id544</t>
+  </si>
+  <si>
+    <t>id545</t>
+  </si>
+  <si>
+    <t>id546</t>
+  </si>
+  <si>
+    <t>id547</t>
+  </si>
+  <si>
+    <t>id548</t>
+  </si>
+  <si>
+    <t>id549</t>
+  </si>
+  <si>
+    <t>id550</t>
+  </si>
+  <si>
+    <t>id551</t>
+  </si>
+  <si>
+    <t>id552</t>
+  </si>
+  <si>
+    <t>id553</t>
+  </si>
+  <si>
+    <t>id554</t>
+  </si>
+  <si>
+    <t>id555</t>
+  </si>
+  <si>
+    <t>id556</t>
+  </si>
+  <si>
+    <t>id557</t>
+  </si>
+  <si>
+    <t>id558</t>
+  </si>
+  <si>
+    <t>id559</t>
+  </si>
+  <si>
+    <t>id560</t>
+  </si>
+  <si>
+    <t>id561</t>
+  </si>
+  <si>
+    <t>id562</t>
+  </si>
+  <si>
+    <t>id563</t>
+  </si>
+  <si>
+    <t>id564</t>
+  </si>
+  <si>
+    <t>id565</t>
+  </si>
+  <si>
+    <t>id566</t>
+  </si>
+  <si>
+    <t>id567</t>
+  </si>
+  <si>
+    <t>id568</t>
+  </si>
+  <si>
+    <t>id569</t>
+  </si>
+  <si>
+    <t>id570</t>
+  </si>
+  <si>
+    <t>id571</t>
+  </si>
+  <si>
+    <t>id572</t>
+  </si>
+  <si>
+    <t>id573</t>
+  </si>
+  <si>
+    <t>id574</t>
+  </si>
+  <si>
+    <t>id575</t>
+  </si>
+  <si>
+    <t>id576</t>
+  </si>
+  <si>
+    <t>id577</t>
+  </si>
+  <si>
+    <t>id578</t>
+  </si>
+  <si>
+    <t>id579</t>
+  </si>
+  <si>
+    <t>id580</t>
+  </si>
+  <si>
+    <t>id581</t>
+  </si>
+  <si>
+    <t>id582</t>
+  </si>
+  <si>
+    <t>id583</t>
+  </si>
+  <si>
+    <t>id584</t>
+  </si>
+  <si>
+    <t>id585</t>
+  </si>
+  <si>
+    <t>id586</t>
+  </si>
+  <si>
+    <t>id587</t>
+  </si>
+  <si>
+    <t>id588</t>
+  </si>
+  <si>
+    <t>id589</t>
+  </si>
+  <si>
+    <t>id590</t>
+  </si>
+  <si>
+    <t>id591</t>
+  </si>
+  <si>
+    <t>id592</t>
+  </si>
+  <si>
+    <t>id593</t>
+  </si>
+  <si>
+    <t>id594</t>
+  </si>
+  <si>
+    <t>id595</t>
+  </si>
+  <si>
+    <t>id596</t>
+  </si>
+  <si>
+    <t>id597</t>
+  </si>
+  <si>
+    <t>id598</t>
   </si>
 </sst>
 </file>
@@ -4010,7 +5809,57 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="52">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -22138,10 +23987,6627 @@
   </sheetData>
   <autoFilter ref="A1:I599"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист10"/>
+  <dimension ref="A1:C599"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C28" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C57" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C61" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C62" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C63" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C64" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C65" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C66" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C67" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C68" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C69" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C70" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C71" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C72" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C73" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C74" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C75" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C76" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C77" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C78" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C79" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C80" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C81" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C82" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C83" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C84" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C85" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C86" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C87" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C88" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C89" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C90" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C91" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C92" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C93" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C94" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C95" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C96" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C97" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C98" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C99" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C100" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C101" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C102" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C103" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C104" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C105" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C106" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C107" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C108" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C109" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C110" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C111" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C112" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C113" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C114" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C115" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C116" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C117" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C118" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C119" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C120" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C121" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C122" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C123" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C124" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C125" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C132" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C151" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C152" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C153" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C154" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C155" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C156" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C157" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C158" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C159" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C160" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C161" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C162" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C163" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C164" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C165" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C166" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C167" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C168" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C169" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C170" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C171" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C172" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C173" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C174" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C175" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C176" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C177" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C178" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C179" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C180" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C181" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C182" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C183" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C184" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C185" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C186" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C187" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C188" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C189" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C190" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C191" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C192" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C193" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C194" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C195" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C196" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C197" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C198" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C199" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C200" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C201" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C202" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C203" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C204" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C205" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C206" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C207" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C208" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C209" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C210" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C211" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C212" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C213" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C214" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C215" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C216" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C217" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C218" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C219" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C220" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C221" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C222" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C223" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C224" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C225" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C226" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C227" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C228" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C229" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C230" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C231" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C232" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C233" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C234" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C235" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C236" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C237" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C238" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C239" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C240" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C241" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C242" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C243" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C244" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C245" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C246" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B247" s="7" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C247" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B248" s="7" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C248" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B249" s="7" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C249" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B250" s="7" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C250" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B251" s="7" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C251" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B252" s="7" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C252" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B253" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C253" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C254" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B255" s="7" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C255" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C256" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C257" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B258" s="7" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C258" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B259" s="7" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C259" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B260" s="7" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C260" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B261" s="7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C261" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B262" s="7" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C262" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B263" s="7" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C263" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B264" s="7" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C264" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B265" s="7" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C265" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B266" s="7" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C266" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B267" s="7" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C267" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B268" s="7" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C268" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B269" s="7" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C269" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C270" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B271" s="7" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C271" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B272" s="7" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C272" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C273" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C274" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C275" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C276" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C277" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C278" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C279" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C280" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C281" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B282" s="7" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C282" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C283" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C284" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C285" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C286" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C287" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C288" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C289" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C290" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B291" s="7" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C291" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B292" s="7" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C292" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C293" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B294" s="7" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C294" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C295" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C296" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C297" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B298" s="7" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C298" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C299" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B300" s="7" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C300" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C301" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C302" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C303" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B304" s="7" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C304" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C305" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C306" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C307" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C308" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C309" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C310" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C311" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C312" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C313" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C314" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C315" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C316" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C317" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C318" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C319" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C320" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C321" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C322" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C323" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C324" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C325" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C326" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C327" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C328" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C329" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C330" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C331" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B332" s="7" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C332" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C333" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C334" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C335" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C336" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C337" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C338" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C339" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C340" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C341" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A342" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C342" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C343" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A344" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C344" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A345" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B345" s="7" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C345" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A346" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C346" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A347" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B347" s="7" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C347" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A348" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C348" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A349" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B349" s="7" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C349" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A350" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B350" s="7" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C350" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B351" s="7" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C351" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A352" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C352" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A353" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B353" s="7" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C353" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A354" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B354" s="7" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C354" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A355" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C355" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A356" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B356" s="7" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C356" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A357" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B357" s="7" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C357" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A358" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B358" s="7" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C358" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B359" s="7" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C359" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B360" s="7" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C360" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B361" s="7" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C361" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A362" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C362" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A363" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C363" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C364" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C365" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C366" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C367" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C368" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C369" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C370" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C371" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C372" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C373" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C374" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C375" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C376" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C377" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C378" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C379" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A380" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C380" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A381" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C381" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A382" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C382" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A383" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C383" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A384" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C384" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A385" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C385" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A386" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C386" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A387" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C387" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A388" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C388" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A389" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C389" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A390" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C390" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A391" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C391" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A392" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C392" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A393" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C393" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A394" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C394" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A395" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C395" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A396" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C396" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A397" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B397" s="7" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C397" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A398" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B398" s="7" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C398" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A399" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B399" s="7" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C399" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A400" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B400" s="7" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C400" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A401" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C401" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A402" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C402" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A403" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B403" s="7" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C403" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A404" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C404" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A405" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C405" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A406" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B406" s="7" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C406" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A407" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C407" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A408" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B408" s="7" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C408" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C409" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C410" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C411" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C412" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B413" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C413" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C414" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B415" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C415" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B416" s="7" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C416" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B417" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C417" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C418" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C419" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C420" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C421" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C422" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C423" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C424" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C425" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B426" s="7" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C426" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B427" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C427" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C428" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C429" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C430" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C431" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C432" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B433" s="7" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C433" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A434" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B434" s="7" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C434" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B435" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C435" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A436" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B436" s="7" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C436" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A437" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C437" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A438" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B438" s="7" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C438" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A439" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B439" s="7" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C439" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A440" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C440" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A441" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C441" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A442" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C442" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A443" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B443" s="7" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C443" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A444" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C444" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A445" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C445" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A446" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B446" s="7" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C446" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A447" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B447" s="7" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C447" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A448" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B448" s="7" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C448" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A449" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C449" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A450" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B450" s="7" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C450" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A451" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B451" s="7" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C451" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A452" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C452" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A453" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C453" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A454" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C454" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A455" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B455" s="7" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C455" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A456" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B456" s="7" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C456" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A457" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B457" s="7" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C457" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A458" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B458" s="7" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C458" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A459" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B459" s="7" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C459" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A460" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C460" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A461" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B461" s="7" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C461" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A462" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C462" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A463" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B463" s="7" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C463" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A464" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B464" s="7" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C464" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A465" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B465" s="7" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C465" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A466" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B466" s="7" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C466" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A467" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B467" s="7" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C467" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B468" s="7" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C468" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A469" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B469" s="7" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C469" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B470" s="7" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C470" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A471" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B471" s="7" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C471" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B472" s="7" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C472" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B473" s="7" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C473" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B474" s="7" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C474" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B475" s="7" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C475" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B476" s="7" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C476" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B477" s="7" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C477" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B478" s="7" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C478" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B479" s="7" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C479" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B480" s="7" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C480" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B481" s="7" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C481" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B482" s="7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C482" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B483" s="7" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C483" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B484" s="7" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C484" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B485" s="7" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C485" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B486" s="7" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C486" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B487" s="7" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C487" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B488" s="7" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C488" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B489" s="7" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C489" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B490" s="7" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C490" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B491" s="7" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C491" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B492" s="7" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C492" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B493" s="7" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C493" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B494" s="7" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C494" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B495" s="7" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C495" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B496" s="7" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C496" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B497" s="7" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C497" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B498" s="7" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C498" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B499" s="7" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C499" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B500" s="7" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C500" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B501" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C501" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B502" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C502" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B503" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C503" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B504" s="7" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C504" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A505" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B505" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C505" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B506" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C506" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A507" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B507" s="7" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C507" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A508" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B508" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C508" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A509" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B509" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C509" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A510" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B510" s="7" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C510" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B511" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C511" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A512" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B512" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C512" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A513" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B513" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C513" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A514" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B514" s="7" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C514" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B515" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C515" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A516" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B516" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C516" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A517" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B517" s="7" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C517" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A518" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B518" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C518" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B519" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C519" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A520" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B520" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C520" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A521" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B521" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C521" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A522" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B522" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C522" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B523" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C523" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A524" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B524" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C524" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A525" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B525" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C525" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A526" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B526" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C526" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B527" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C527" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A528" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B528" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C528" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B529" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C529" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B530" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C530" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B531" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C531" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B532" s="7" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C532" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B533" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C533" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B534" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C534" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B535" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C535" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B536" s="7" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C536" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B537" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C537" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B538" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C538" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C539" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B540" s="7" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C540" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C541" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B542" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C542" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B543" s="7" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C543" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B544" s="7" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C544" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B545" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C545" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B546" s="7" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C546" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B547" s="7" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C547" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B548" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C548" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A549" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B549" s="7" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C549" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B550" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C550" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B551" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C551" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B552" s="7" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C552" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A553" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B553" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C553" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B554" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C554" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B555" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C555" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A556" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B556" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C556" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B557" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C557" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B558" s="7" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C558" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A559" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B559" s="7" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C559" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B560" s="7" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C560" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B561" s="7" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C561" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B562" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C562" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B563" s="7" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C563" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A564" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B564" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C564" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B565" s="7" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C565" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B566" s="7" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C566" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B567" s="7" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C567" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B568" s="7" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C568" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B569" s="7" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C569" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B570" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C570" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B571" s="7" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C571" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B572" s="7" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C572" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B573" s="7" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C573" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B574" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C574" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B575" s="7" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C575" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A576" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B576" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C576" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B577" s="7" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C577" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B578" s="7" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C578" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B579" s="7" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C579" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B580" s="7" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C580" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A581" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B581" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C581" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B582" s="7" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C582" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B583" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C583" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B584" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C584" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B585" s="7" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C585" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B586" s="7" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C586" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A587" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B587" s="7" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C587" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A588" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B588" s="7" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C588" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A589" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B589" s="7" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C589" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A590" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B590" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C590" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A591" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B591" s="7" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C591" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A592" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B592" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C592" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A593" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B593" s="7" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C593" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A594" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B594" s="7" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C594" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A595" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B595" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C595" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A596" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B596" s="7" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C596" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A597" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B597" s="7" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C597" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A598" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B598" s="7" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C598" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A599" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B599" s="7" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C599" s="7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C1"/>
+  <conditionalFormatting sqref="A2:A599">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1 A600:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -28772,22 +37238,22 @@
   </sheetData>
   <autoFilter ref="B1:C601"/>
   <conditionalFormatting sqref="B2:B599 B602:B1048576">
-    <cfRule type="duplicateValues" dxfId="44" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B600:B601">
-    <cfRule type="duplicateValues" dxfId="43" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="42" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35418,22 +43884,22 @@
   </sheetData>
   <autoFilter ref="A1:C601"/>
   <conditionalFormatting sqref="A2:B2 A602:B1048576 A3:A599 B3:B601">
-    <cfRule type="duplicateValues" dxfId="38" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600:A601">
-    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -42723,31 +51189,31 @@
   </sheetData>
   <autoFilter ref="A1:C661"/>
   <conditionalFormatting sqref="A2:B2 A662:B1048576 A3:A599 B3:B661">
-    <cfRule type="duplicateValues" dxfId="32" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600">
-    <cfRule type="duplicateValues" dxfId="31" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A601">
-    <cfRule type="duplicateValues" dxfId="30" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A602">
-    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A603:A608">
-    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A609:A614">
-    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A615:A661">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49620,22 +58086,22 @@
   </sheetData>
   <autoFilter ref="A1:C623"/>
   <conditionalFormatting sqref="A2:A599 A624:A1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600:A603">
-    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A604:A607">
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A608:A623">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -56310,22 +64776,22 @@
   </sheetData>
   <autoFilter ref="A1:C605"/>
   <conditionalFormatting sqref="A2:A599 A606:A1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600:A603">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A604">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A605">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -62945,16 +71411,16 @@
   </sheetData>
   <autoFilter ref="A1:C600"/>
   <conditionalFormatting sqref="A2:A599 A601:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -69574,16 +78040,16 @@
   </sheetData>
   <autoFilter ref="A1:C600"/>
   <conditionalFormatting sqref="A2:A599 A601:A1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -76302,16 +84768,16 @@
   </sheetData>
   <autoFilter ref="A1:C609"/>
   <conditionalFormatting sqref="A2:A599 A610:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A600:A609">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
